--- a/DesignData/Excel_Masters/EnemyBasicAttackStats_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyBasicAttackStats_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23625" windowHeight="10380"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyBasicAttackStats" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <t>ProjectileDataHandle</t>
   </si>
   <si>
-    <t>M_Balrog_Atk</t>
+    <t>Balrog</t>
   </si>
   <si>
     <t>Enemy</t>
@@ -69,142 +69,142 @@
     <t>(DataTable=None,RowName="")</t>
   </si>
   <si>
-    <t>M_Bearking_Atk</t>
-  </si>
-  <si>
-    <t>M_BombSpider_Atk</t>
-  </si>
-  <si>
-    <t>M_BronzeGear_Atk</t>
-  </si>
-  <si>
-    <t>M_Cell_Atk</t>
-  </si>
-  <si>
-    <t>M_Cursedmass_Atk</t>
-  </si>
-  <si>
-    <t>M_DanceMakane_Atk</t>
-  </si>
-  <si>
-    <t>M_Deatheye_Atk</t>
-  </si>
-  <si>
-    <t>M_DieS_Atk</t>
-  </si>
-  <si>
-    <t>M_DoctorMacaron_Atk</t>
-  </si>
-  <si>
-    <t>M_Famine_Atk</t>
-  </si>
-  <si>
-    <t>M_FelicisMachine_Atk</t>
-  </si>
-  <si>
-    <t>M_FelicisShinobi_Atk</t>
-  </si>
-  <si>
-    <t>M_Fiti_Atk</t>
-  </si>
-  <si>
-    <t>M_Gemini_Scythe_Atk</t>
-  </si>
-  <si>
-    <t>M_GhostMacaron_Atk</t>
-  </si>
-  <si>
-    <t>M_Graf_Atk</t>
-  </si>
-  <si>
-    <t>M_GuardianTreant_Atk</t>
-  </si>
-  <si>
-    <t>M_HackingTool_Atk</t>
-  </si>
-  <si>
-    <t>M_Hanged_Macaron_Atk</t>
-  </si>
-  <si>
-    <t>M_HoneyMos_Atk</t>
-  </si>
-  <si>
-    <t>M_Jellyfish_Atk</t>
-  </si>
-  <si>
-    <t>M_Karakasa_Atk</t>
-  </si>
-  <si>
-    <t>M_Kraken_Atk</t>
-  </si>
-  <si>
-    <t>M_KrakenTentacle_Atk</t>
-  </si>
-  <si>
-    <t>M_Leechking_Atk</t>
-  </si>
-  <si>
-    <t>M_LikeStatue_Atk</t>
-  </si>
-  <si>
-    <t>M_LordFelice_Atk</t>
-  </si>
-  <si>
-    <t>M_Makane_Atk</t>
-  </si>
-  <si>
-    <t>M_Mandragora_Atk</t>
-  </si>
-  <si>
-    <t>M_MaskScarecrow_Atk</t>
-  </si>
-  <si>
-    <t>M_Mechanicus_Atk</t>
-  </si>
-  <si>
-    <t>M_Megaron_Atk</t>
-  </si>
-  <si>
-    <t>M_Mimic_Atk</t>
-  </si>
-  <si>
-    <t>M_Octopus_Atk</t>
-  </si>
-  <si>
-    <t>M_PistolShrimp_Atk</t>
-  </si>
-  <si>
-    <t>M_Pufferfish_Atk</t>
-  </si>
-  <si>
-    <t>M_Seasoner_Atk</t>
-  </si>
-  <si>
-    <t>M_SharkRider_Atk</t>
-  </si>
-  <si>
-    <t>M_SoundPro_Atk</t>
-  </si>
-  <si>
-    <t>M_Starspawn_Atk</t>
-  </si>
-  <si>
-    <t>M_TinWoodman_Atk</t>
-  </si>
-  <si>
-    <t>M_Ushabti_Atk</t>
-  </si>
-  <si>
-    <t>M_Wagon_Atk</t>
-  </si>
-  <si>
-    <t>M_Watcher_Atk</t>
-  </si>
-  <si>
-    <t>M_Weaponmaster_Atk</t>
-  </si>
-  <si>
-    <t>M_Wolfron_Atk</t>
+    <t>Bearking</t>
+  </si>
+  <si>
+    <t>BombSpider</t>
+  </si>
+  <si>
+    <t>BronzeGear</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Cursedmass</t>
+  </si>
+  <si>
+    <t>DanceMakane</t>
+  </si>
+  <si>
+    <t>Deatheye</t>
+  </si>
+  <si>
+    <t>DieS</t>
+  </si>
+  <si>
+    <t>DoctorMacaron</t>
+  </si>
+  <si>
+    <t>Famine</t>
+  </si>
+  <si>
+    <t>FelicisMachine</t>
+  </si>
+  <si>
+    <t>FelicisShinobi</t>
+  </si>
+  <si>
+    <t>Fiti</t>
+  </si>
+  <si>
+    <t>Gemini_Scythe</t>
+  </si>
+  <si>
+    <t>GhostMacaron</t>
+  </si>
+  <si>
+    <t>Graf</t>
+  </si>
+  <si>
+    <t>GuardianTreant</t>
+  </si>
+  <si>
+    <t>HackingTool</t>
+  </si>
+  <si>
+    <t>Hanged_Macaron</t>
+  </si>
+  <si>
+    <t>HoneyMos</t>
+  </si>
+  <si>
+    <t>Jellyfish</t>
+  </si>
+  <si>
+    <t>Karakasa</t>
+  </si>
+  <si>
+    <t>Kraken</t>
+  </si>
+  <si>
+    <t>KrakenTentacle</t>
+  </si>
+  <si>
+    <t>Leechking</t>
+  </si>
+  <si>
+    <t>LikeStatue</t>
+  </si>
+  <si>
+    <t>LordFelice</t>
+  </si>
+  <si>
+    <t>Makane</t>
+  </si>
+  <si>
+    <t>Mandragora</t>
+  </si>
+  <si>
+    <t>MaskScarecrow</t>
+  </si>
+  <si>
+    <t>Mechanicus</t>
+  </si>
+  <si>
+    <t>Megaron</t>
+  </si>
+  <si>
+    <t>Mimic</t>
+  </si>
+  <si>
+    <t>Octopus</t>
+  </si>
+  <si>
+    <t>PistolShrimp</t>
+  </si>
+  <si>
+    <t>Pufferfish</t>
+  </si>
+  <si>
+    <t>Seasoner</t>
+  </si>
+  <si>
+    <t>SharkRider</t>
+  </si>
+  <si>
+    <t>SoundPro</t>
+  </si>
+  <si>
+    <t>Starspawn</t>
+  </si>
+  <si>
+    <t>TinWoodman</t>
+  </si>
+  <si>
+    <t>Ushabti</t>
+  </si>
+  <si>
+    <t>Wagon</t>
+  </si>
+  <si>
+    <t>Watcher</t>
+  </si>
+  <si>
+    <t>Weaponmaster</t>
+  </si>
+  <si>
+    <t>Wolfron</t>
   </si>
 </sst>
 </file>
